--- a/output/pdf_financials_xlsx/AAB.xlsx
+++ b/output/pdf_financials_xlsx/AAB.xlsx
@@ -1010,49 +1010,49 @@
         <v>0</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0</v>
+        <v>15.140272</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0</v>
+        <v>14.753494</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0</v>
+        <v>9.268966000000001</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0</v>
+        <v>11.042297</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0</v>
+        <v>3.470749</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0</v>
+        <v>5.09996</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0</v>
+        <v>5.966545</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0</v>
+        <v>1.806803</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0</v>
+        <v>1.912631</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0</v>
+        <v>2.768255</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>0</v>
+        <v>8.29731</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>0</v>
+        <v>4.396331</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>0</v>
+        <v>2.622683</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>0</v>
+        <v>1.995425</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>0</v>
+        <v>1.457954</v>
       </c>
     </row>
     <row r="11">
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>1.610644</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.767715</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
@@ -1166,31 +1166,31 @@
         <v>0.103449</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.271162</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.358292</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.407679</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.298153</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.268024</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.097972</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.057789</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>0.051932</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>0</v>
+        <v>0.111506</v>
       </c>
     </row>
     <row r="13">
@@ -2208,10 +2208,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-14.055254</v>
+        <v>-15.665898</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>28.271102</v>
+        <v>27.503387</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>34.840202</v>
@@ -2235,31 +2235,31 @@
         <v>9.693356</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>16.569549</v>
+        <v>16.298387</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-25.953677</v>
+        <v>-26.311969</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>1.868523</v>
+        <v>1.460844</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>2.918027</v>
+        <v>2.619874</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>0.900935</v>
+        <v>0.632911</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-13.097449</v>
+        <v>-13.195421</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-17.797881</v>
+        <v>-17.85567</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-8.898928</v>
+        <v>-8.95086</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>-2.154858</v>
+        <v>-2.266364</v>
       </c>
     </row>
     <row r="28">
@@ -2330,10 +2330,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-14.055254</v>
+        <v>-15.665898</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>28.271102</v>
+        <v>27.503387</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>34.840202</v>
@@ -2357,31 +2357,31 @@
         <v>9.693356</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>16.569549</v>
+        <v>16.298387</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-25.953677</v>
+        <v>-26.311969</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>1.868523</v>
+        <v>1.460844</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>2.918027</v>
+        <v>2.619874</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>0.900935</v>
+        <v>0.632911</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-13.097449</v>
+        <v>-13.195421</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-17.797881</v>
+        <v>-17.85567</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-8.898928</v>
+        <v>-8.95086</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>-2.154858</v>
+        <v>-2.266364</v>
       </c>
     </row>
     <row r="30">
@@ -2659,52 +2659,52 @@
         <v>3.266356</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>14.049856</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>7.372118</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.322185</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.868267</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.355188</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.604613</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.626293</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.306086</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.128134</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.176973</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.106381</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>2.048529</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.039083</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.06748700000000001</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.12718</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>0</v>
+        <v>0.009316</v>
       </c>
     </row>
     <row r="35">
@@ -2781,52 +2781,52 @@
         <v>3.266356</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>14.049856</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>7.372118</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.322185</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.868267</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.355188</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.604613</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.626293</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.306086</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.128134</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.176973</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.106381</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>2.048529</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.039083</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.06748700000000001</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.12718</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>0</v>
+        <v>0.009316</v>
       </c>
     </row>
     <row r="37">
@@ -3513,10 +3513,10 @@
         <v>69.462682</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>130.354231</v>
+        <v>116.304375</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>79.85323699999999</v>
+        <v>72.48111900000001</v>
       </c>
       <c r="F48" s="3" t="n">
         <v>0</v>
@@ -9292,7 +9292,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -11022,7 +11022,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -12038,7 +12038,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -15760,7 +15760,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -19972,7 +19972,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -21322,7 +21322,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -64404,7 +64404,7 @@
       </c>
       <c r="D533" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E533" t="inlineStr">
@@ -64768,7 +64768,7 @@
       </c>
       <c r="D537" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E537" t="inlineStr">
@@ -64958,7 +64958,7 @@
       </c>
       <c r="D539" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E539" t="inlineStr">
@@ -68264,7 +68264,7 @@
       </c>
       <c r="D571" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E571" t="inlineStr">
@@ -69842,7 +69842,7 @@
       </c>
       <c r="D586" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E586" t="inlineStr">
@@ -72536,7 +72536,7 @@
       </c>
       <c r="D612" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E612" t="inlineStr">
@@ -74098,7 +74098,7 @@
       </c>
       <c r="D627" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E627" t="inlineStr">
@@ -75258,7 +75258,7 @@
       </c>
       <c r="D638" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E638" t="inlineStr">
@@ -76746,7 +76746,7 @@
       </c>
       <c r="D652" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E652" t="inlineStr">
@@ -78546,7 +78546,7 @@
       </c>
       <c r="D669" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E669" t="inlineStr">
@@ -85530,7 +85530,7 @@
       </c>
       <c r="D735" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E735" s="5" t="n">

--- a/output/pdf_financials_xlsx/AAB.xlsx
+++ b/output/pdf_financials_xlsx/AAB.xlsx
@@ -1444,25 +1444,25 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>5.003875</v>
+        <v>1.092125</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>-6.656109</v>
+        <v>-1.347891</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>-0</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>13.993525</v>
+        <v>-13.993525</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>6.098597</v>
+        <v>-6.098597</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>6.209972</v>
+        <v>-6.209972</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>0.167343</v>
+        <v>-0.167343</v>
       </c>
       <c r="I17" s="3" t="n">
         <v>-0</v>
@@ -2488,10 +2488,10 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>-35.60145551265029</v>
+        <v>-7.770225995204355</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>23.54386114839103</v>
+        <v>4.767734204347605</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>0</v>
@@ -4594,10 +4594,10 @@
         <v>0</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0</v>
+        <v>0.151673</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0</v>
+        <v>1.45448</v>
       </c>
       <c r="I64" s="3" t="n">
         <v>0</v>
@@ -4765,46 +4765,46 @@
         <v>0</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.132294</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.550803</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.406442</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.289426</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.76881</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>2.24658</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.808484</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.773663</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>2.822782</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>0.110371</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>0.14076</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>0.7128679999999999</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>0</v>
+        <v>0.65</v>
       </c>
       <c r="P67" s="3" t="n">
-        <v>0</v>
+        <v>0.54178</v>
       </c>
       <c r="Q67" s="3" t="n">
         <v>0</v>
@@ -7476,10 +7476,10 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.059835</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.011232</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>0</v>
@@ -8931,10 +8931,10 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.059835</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.011232</v>
       </c>
       <c r="D134" s="3" t="n">
         <v>0</v>
@@ -8992,10 +8992,10 @@
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>4.236226</v>
+        <v>4.176391</v>
       </c>
       <c r="C135" s="3" t="n">
-        <v>-0.255113</v>
+        <v>-0.266345</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>-1.106888</v>
@@ -41970,7 +41970,11 @@
           <t>Private placement</t>
         </is>
       </c>
-      <c r="D320" t="inlineStr"/>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E320" t="inlineStr">
         <is>
           <t>-</t>
@@ -48014,7 +48018,11 @@
           <t>Private placement 11</t>
         </is>
       </c>
-      <c r="D378" t="inlineStr"/>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E378" t="inlineStr">
         <is>
           <t>-</t>
@@ -49068,7 +49076,11 @@
           <t>Private placement 10</t>
         </is>
       </c>
-      <c r="D388" t="inlineStr"/>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E388" t="inlineStr">
         <is>
           <t>-</t>
@@ -58054,7 +58066,11 @@
           <t>Future income taxes</t>
         </is>
       </c>
-      <c r="D473" t="inlineStr"/>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E473" t="inlineStr">
         <is>
           <t>-</t>
@@ -59530,7 +59546,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D487" t="inlineStr"/>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E487" s="5" t="n">
         <v>-0.059835</v>
       </c>
@@ -61442,7 +61462,11 @@
           <t>Future income tax</t>
         </is>
       </c>
-      <c r="D505" t="inlineStr"/>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E505" s="5" t="n">
         <v>-6.096</v>
       </c>
@@ -75688,7 +75712,11 @@
           <t>Income tax recovery 10</t>
         </is>
       </c>
-      <c r="D642" t="inlineStr"/>
+      <c r="D642" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E642" t="inlineStr">
         <is>
           <t>-</t>
@@ -77176,7 +77204,11 @@
           <t>Income tax recovery 8</t>
         </is>
       </c>
-      <c r="D656" t="inlineStr"/>
+      <c r="D656" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E656" t="inlineStr">
         <is>
           <t>-</t>
@@ -78976,7 +79008,11 @@
           <t>Income tax recovery 9</t>
         </is>
       </c>
-      <c r="D673" t="inlineStr"/>
+      <c r="D673" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E673" t="inlineStr">
         <is>
           <t>-</t>
@@ -80874,7 +80910,11 @@
           <t>Income tax recovery 9</t>
         </is>
       </c>
-      <c r="D691" t="inlineStr"/>
+      <c r="D691" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E691" t="inlineStr">
         <is>
           <t>-</t>
@@ -86588,7 +86628,11 @@
           <t>Current income tax recovery (expense)</t>
         </is>
       </c>
-      <c r="D745" t="inlineStr"/>
+      <c r="D745" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E745" s="5" t="n">
         <v>-1.092125</v>
       </c>
